--- a/docs/gamepad_wireless_BOM.xlsx
+++ b/docs/gamepad_wireless_BOM.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="19" min="1" max="1"/>
@@ -745,12 +745,12 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>USB Type-A メスコネクタ DIP化基板</t>
+          <t>USB Type-A メスコネクタ（基板直付け・横型）</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>AE-USB-A-DIP 相当</t>
+          <t>DS1095-WNR0 相当</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="H7" s="28">
         <f>F7*G7</f>
@@ -775,12 +775,12 @@
       </c>
       <c r="I7" s="29" t="inlineStr">
         <is>
-          <t>秋月電子 税込価格(参考)</t>
+          <t>概算</t>
         </is>
       </c>
       <c r="J7" s="29" t="inlineStr">
         <is>
-          <t>ゲームパッド接続用。VBUSはXIAOの5Vピンから</t>
+          <t>変換基板は使わず基板に直付け。フットプリントは USB_A_CONNFLY_DS1095-WNR0</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>ユニバーサル基板（小型）</t>
+          <t>モバイルバッテリー（5V USB出力）</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
@@ -896,19 +896,19 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>要検索</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="F10" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H10" s="28">
         <f>F10*G10</f>
@@ -916,10 +916,14 @@
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>概算</t>
-        </is>
-      </c>
-      <c r="J10" s="29" t="n"/>
+          <t>手持ち流用想定</t>
+        </is>
+      </c>
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>XIAOのUSB-Cへ給電。低電流で自動OFFしない機種が望ましい</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17.15" customHeight="1" s="20">
       <c r="A11" s="24" t="inlineStr">
@@ -929,7 +933,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>ピンヘッダ／ピンソケット 2.54mm</t>
+          <t>USBケーブル（バッテリー→XIAO USB-C）</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
@@ -939,19 +943,19 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>要検索</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H11" s="28">
         <f>F11*G11</f>
@@ -959,46 +963,42 @@
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>概算</t>
-        </is>
-      </c>
-      <c r="J11" s="30" t="inlineStr">
-        <is>
-          <t>XIAO・IM920SL実装用</t>
-        </is>
-      </c>
+          <t>手持ち流用想定</t>
+        </is>
+      </c>
+      <c r="J11" s="30" t="n"/>
     </row>
     <row r="12" ht="32.8" customHeight="1" s="20">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>送信側</t>
+          <t>受信側</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>モバイルバッテリー（5V USB出力）</t>
+          <t>Seeed XIAO RP2040</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102010428</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2229736</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="F12" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="H12" s="28">
         <f>F12*G12</f>
@@ -1006,46 +1006,46 @@
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>手持ち流用想定</t>
+          <t>秋月電子 税込価格(参考)</t>
         </is>
       </c>
       <c r="J12" s="30" t="inlineStr">
         <is>
-          <t>XIAOのUSB-Cへ給電。低電流で自動OFFしない機種が望ましい</t>
+          <t>ネイティブUSBでHIDゲームパッドとしてPCに接続</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32.8" customHeight="1" s="20">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>送信側</t>
+          <t>受信側</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>USBケーブル（バッテリー→XIAO USB-C）</t>
+          <t>920MHz無線モジュール（ワイヤーアンテナ）</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IM920SL</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2218859</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>0</v>
+        <v>4750</v>
       </c>
       <c r="H13" s="28">
         <f>F13*G13</f>
@@ -1053,10 +1053,14 @@
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>手持ち流用想定</t>
-        </is>
-      </c>
-      <c r="J13" s="29" t="n"/>
+          <t>マルツ定価(2023年キャンペーン告知)</t>
+        </is>
+      </c>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>親機（ノード0001）。UARTはGPIO0/1</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17.15" customHeight="1" s="20">
       <c r="A14" s="24" t="inlineStr">
@@ -1066,29 +1070,29 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Seeed XIAO RP2040</t>
+          <t>USB-Cケーブル（PC接続）</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>102010428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>2229736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="F14" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="H14" s="28">
         <f>F14*G14</f>
@@ -1096,46 +1100,42 @@
       </c>
       <c r="I14" s="29" t="inlineStr">
         <is>
-          <t>秋月電子 税込価格(参考)</t>
-        </is>
-      </c>
-      <c r="J14" s="29" t="inlineStr">
-        <is>
-          <t>ネイティブUSBでHIDゲームパッドとしてPCに接続</t>
-        </is>
-      </c>
+          <t>手持ち流用想定</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="n"/>
     </row>
     <row r="15" ht="32.8" customHeight="1" s="20">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>受信側</t>
+          <t>共通・開発用</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>920MHz無線モジュール（ワイヤーアンテナ）</t>
+          <t>USBインタフェースボード</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>IM920SL</t>
+          <t>IM920-USB2</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>2218859</t>
+          <t>要検索</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="F15" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>4750</v>
+        <v>2500</v>
       </c>
       <c r="H15" s="28">
         <f>F15*G15</f>
@@ -1148,19 +1148,19 @@
       </c>
       <c r="J15" s="29" t="inlineStr">
         <is>
-          <t>親機（ノード0001）。UARTはGPIO0/1</t>
+          <t>不要（XIAOのUSBブリッジで代替）。数量0で集計外</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17.15" customHeight="1" s="20">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>受信側</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>ユニバーサル基板（小型）</t>
+          <t>積層セラミックコンデンサ 10µF（C2）</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="F16" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="H16" s="28">
         <f>F16*G16</f>
@@ -1193,17 +1193,21 @@
           <t>概算</t>
         </is>
       </c>
-      <c r="J16" s="29" t="n"/>
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>IM920SL VCC 直近（送信機・受信機に各1）</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17.15" customHeight="1" s="20">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>受信側</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>ピンヘッダ／ピンソケット 2.54mm</t>
+          <t>積層セラミックコンデンサ 0.1µF（C3）</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
@@ -1222,10 +1226,10 @@
         </is>
       </c>
       <c r="F17" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H17" s="28">
         <f>F17*G17</f>
@@ -1236,39 +1240,43 @@
           <t>概算</t>
         </is>
       </c>
-      <c r="J17" s="29" t="n"/>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>IM920SL VCC 直近（各1）</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17.15" customHeight="1" s="20">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>受信側</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>USB-Cケーブル（PC接続）</t>
+          <t>IM920sL用変換アダプタ（2.54mm J1/J2）</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IM920sL-ADP</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>要検索</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="F18" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H18" s="28">
         <f>F18*G18</f>
@@ -1276,42 +1284,46 @@
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>手持ち流用想定</t>
-        </is>
-      </c>
-      <c r="J18" s="29" t="n"/>
+          <t>仮置き（旧IM920C-ADPの2023年定価）</t>
+        </is>
+      </c>
+      <c r="J18" s="29" t="inlineStr">
+        <is>
+          <t>IM920sLの20ピンコネクタを2.54mmピッチに変換。販売状況・価格を要確認</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26.85" customHeight="1" s="20">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>共通・開発用</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>USBインタフェースボード</t>
+          <t>プリント基板（本リポジトリのガーバー）</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>IM920-USB2</t>
+          <t>100×62mm 2層 t1.6</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>要検索</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>必須</t>
         </is>
       </c>
       <c r="F19" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="H19" s="28">
         <f>F19*G19</f>
@@ -1319,12 +1331,12 @@
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>マルツ定価(2023年キャンペーン告知)</t>
+          <t>JLCPCB 等の概算</t>
         </is>
       </c>
       <c r="J19" s="29" t="inlineStr">
         <is>
-          <t>不要（XIAOのUSBブリッジで代替）。数量0で集計外</t>
+          <t>送信機・受信機で同じ基板。hardware/board/gamepad_over_920MHz-gerber.zip を発注。最小 5 枚で送料込 ¥1,500〜4,000</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1348,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>積層セラミックコンデンサ 10µF（C2）</t>
+          <t>ピンヘッダ 1×10 2.54mm（ADP 側）</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -1355,10 +1367,10 @@
         </is>
       </c>
       <c r="F20" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H20" s="28">
         <f>F20*G20</f>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="J20" s="30" t="inlineStr">
         <is>
-          <t>IM920SL VCC 直近（送信機・受信機に各1）</t>
+          <t>ADP に実装して基板のソケットへ挿す。1×40 の連結品を切って使う</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1395,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>積層セラミックコンデンサ 0.1µF（C3）</t>
+          <t>ピンソケット 1×10 2.54mm（基板側・ADP 受け）</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
@@ -1402,10 +1414,10 @@
         </is>
       </c>
       <c r="F21" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H21" s="28">
         <f>F21*G21</f>
@@ -1418,7 +1430,7 @@
       </c>
       <c r="J21" s="30" t="inlineStr">
         <is>
-          <t>IM920SL VCC 直近（各1）</t>
+          <t>ADP は裏面にコネクタが出るので、ソケットで嵩上げする</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1442,12 @@
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>IM920sL用変換アダプタ（2.54mm J1/J2）</t>
+          <t>ピンソケット 1×7 2.54mm（基板側・XIAO 受け）</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>IM920sL-ADP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -1449,35 +1461,35 @@
         </is>
       </c>
       <c r="F22" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>1400</v>
+        <v>45</v>
       </c>
       <c r="H22" s="28">
-        <f>F23*G23</f>
+        <f>F22*G22</f>
         <v/>
       </c>
       <c r="I22" s="29" t="inlineStr">
         <is>
-          <t>仮置き（旧IM920C-ADPの2023年定価）</t>
+          <t>概算</t>
         </is>
       </c>
       <c r="J22" s="30" t="inlineStr">
         <is>
-          <t>IM920sLの20ピンコネクタを2.54mmピッチに変換。販売状況・価格を要確認</t>
+          <t>XIAO を抜き差しできるようにする</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32.8" customHeight="1" s="20">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>共通・開発用</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>ジャンパワイヤ・ブレッドボード</t>
+          <t>ピンヘッダ 1×7 2.54mm（XIAO 側）</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
@@ -1487,7 +1499,7 @@
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>要検索</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -1496,124 +1508,214 @@
         </is>
       </c>
       <c r="F23" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H23" s="28">
-        <f>F25*G25</f>
+        <f>F23*G23</f>
         <v/>
       </c>
       <c r="I23" s="29" t="inlineStr">
         <is>
-          <t>手持ち流用想定</t>
+          <t>概算</t>
         </is>
       </c>
       <c r="J23" s="29" t="inlineStr">
         <is>
-          <t>試作用</t>
+          <t>XIAO RP2040 に 2 本付属するので通常は不要。無い場合は 4 本（数量0で集計外）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17.15" customHeight="1" s="20">
       <c r="A24" s="24" t="inlineStr">
         <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>M3 ネジ・スペーサー</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>要検索</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="28">
+        <f>F24*G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="29" t="inlineStr">
+        <is>
+          <t>概算</t>
+        </is>
+      </c>
+      <c r="J24" s="29" t="inlineStr">
+        <is>
+          <t>基板四隅の φ3.2 固定穴用。ケースに留める場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17.15" customHeight="1" s="20">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>共通・開発用</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>ジャンパワイヤ・ブレッドボード</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="28">
+        <f>F25*G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="29" t="inlineStr">
+        <is>
+          <t>手持ち流用想定</t>
+        </is>
+      </c>
+      <c r="J25" s="30" t="inlineStr">
+        <is>
+          <t>試作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32.8" customHeight="1" s="20">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
           <t>将来・距離延長</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>920MHz無線モジュール（外部アンテナタイプ）</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
         <is>
           <t>IM920SL-XT</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>2218863</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G26" s="27" t="n">
         <v>7600</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H26" s="28">
         <f>F26*G26</f>
         <v/>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>マルツ定価(2023年キャンペーン告知)</t>
         </is>
       </c>
-      <c r="J24" s="29" t="inlineStr">
+      <c r="J26" s="30" t="inlineStr">
         <is>
           <t>距離不足時にIM920SLと置き換え（数量0で集計外）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="17.15" customHeight="1" s="20"/>
-    <row r="26" ht="32.8" customHeight="1" s="20">
-      <c r="G26" s="31" t="inlineStr">
-        <is>
-          <t>必須部品 合計</t>
-        </is>
-      </c>
-      <c r="H26" s="32">
-        <f>SUMIFS(H5:H24,E5:E24,"必須")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27">
-      <c r="G27" s="31" t="inlineStr">
-        <is>
-          <t>任意部品 合計</t>
-        </is>
-      </c>
-      <c r="H27" s="32">
-        <f>SUMIFS(H5:H24,E5:E24,"任意")</f>
-        <v/>
-      </c>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="32" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="20">
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>総計</t>
+          <t>必須部品 合計</t>
         </is>
       </c>
       <c r="H28" s="32">
-        <f>SUM(H5:H24)</f>
+        <f>SUMIFS(H5:H26,E5:E26,"必須")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="20">
       <c r="G29" s="31" t="inlineStr">
         <is>
+          <t>任意部品 合計</t>
+        </is>
+      </c>
+      <c r="H29" s="32">
+        <f>SUMIFS(H5:H26,E5:E26,"任意")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="20">
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>総計</t>
+        </is>
+      </c>
+      <c r="H30" s="19">
+        <f>SUM(H5:H26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="17.15" customHeight="1" s="20">
+      <c r="A31" s="33" t="n"/>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
           <t>送料無料までの残額（マルツ：3,000円以上で送料無料）</t>
         </is>
       </c>
-      <c r="H29" s="32">
-        <f>MAX(0,3000-H28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="20"/>
-    <row r="31" ht="17.15" customHeight="1" s="20">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>注記：</t>
-        </is>
+      <c r="H31" s="19">
+        <f>MAX(0,3000-H30)</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1652,22 +1754,19 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="20">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>・Rev.3：タクトスイッチ（SW1）と STATUS LED は削除。設定/ペアリングは XIAO の BOOTSEL、</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="20">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">　状態表示は XIAO オンボードのカラー LED を使うため不要。</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
   </sheetData>
   <autoFilter ref="A4:J26"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2159,34 +2258,34 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>設定/ペアリング＝XIAO の BOOTSEL ボタン</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>SW1 は廃止（起動後 5 秒の受付ウィンドウ、または赤点滅中に長押し）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>状態表示＝XIAO オンボードのカラー LED</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>NeoPixel(GPIO12/電源GPIO11) と三色 LED(R17/G16/B25)。STATUS LED は廃止</t>
         </is>
